--- a/artfynd/A 13873-2026 artfynd.xlsx
+++ b/artfynd/A 13873-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131726429</v>
       </c>
       <c r="B2" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131726431</v>
       </c>
       <c r="B3" t="n">
-        <v>96624</v>
+        <v>96625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>131737833</v>
       </c>
       <c r="B4" t="n">
-        <v>96624</v>
+        <v>96625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131726428</v>
       </c>
       <c r="B5" t="n">
-        <v>79879</v>
+        <v>79880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13873-2026 artfynd.xlsx
+++ b/artfynd/A 13873-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131726429</v>
       </c>
       <c r="B2" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131726431</v>
       </c>
       <c r="B3" t="n">
-        <v>96625</v>
+        <v>96628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>131737833</v>
       </c>
       <c r="B4" t="n">
-        <v>96625</v>
+        <v>96628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131726428</v>
       </c>
       <c r="B5" t="n">
-        <v>79880</v>
+        <v>79883</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13873-2026 artfynd.xlsx
+++ b/artfynd/A 13873-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131726429</v>
       </c>
       <c r="B2" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131726431</v>
       </c>
       <c r="B3" t="n">
-        <v>96628</v>
+        <v>96634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>131737833</v>
       </c>
       <c r="B4" t="n">
-        <v>96628</v>
+        <v>96634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131726428</v>
       </c>
       <c r="B5" t="n">
-        <v>79883</v>
+        <v>79885</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13873-2026 artfynd.xlsx
+++ b/artfynd/A 13873-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131726429</v>
       </c>
       <c r="B2" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131726431</v>
       </c>
       <c r="B3" t="n">
-        <v>96634</v>
+        <v>96637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>131737833</v>
       </c>
       <c r="B4" t="n">
-        <v>96634</v>
+        <v>96637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131726428</v>
       </c>
       <c r="B5" t="n">
-        <v>79885</v>
+        <v>79888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13873-2026 artfynd.xlsx
+++ b/artfynd/A 13873-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131726429</v>
       </c>
       <c r="B2" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131726431</v>
       </c>
       <c r="B3" t="n">
-        <v>96637</v>
+        <v>96642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>131737833</v>
       </c>
       <c r="B4" t="n">
-        <v>96637</v>
+        <v>96642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131726428</v>
       </c>
       <c r="B5" t="n">
-        <v>79888</v>
+        <v>79893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13873-2026 artfynd.xlsx
+++ b/artfynd/A 13873-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131726429</v>
       </c>
       <c r="B2" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131726431</v>
       </c>
       <c r="B3" t="n">
-        <v>96642</v>
+        <v>96644</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>131737833</v>
       </c>
       <c r="B4" t="n">
-        <v>96642</v>
+        <v>96644</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131726428</v>
       </c>
       <c r="B5" t="n">
-        <v>79893</v>
+        <v>79895</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13873-2026 artfynd.xlsx
+++ b/artfynd/A 13873-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131726429</v>
       </c>
       <c r="B2" t="n">
-        <v>79895</v>
+        <v>79929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131726431</v>
       </c>
       <c r="B3" t="n">
-        <v>96644</v>
+        <v>96680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>131737833</v>
       </c>
       <c r="B4" t="n">
-        <v>96644</v>
+        <v>96680</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131726428</v>
       </c>
       <c r="B5" t="n">
-        <v>79895</v>
+        <v>79929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13873-2026 artfynd.xlsx
+++ b/artfynd/A 13873-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131726429</v>
       </c>
       <c r="B2" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>131726431</v>
       </c>
       <c r="B3" t="n">
-        <v>96685</v>
+        <v>96688</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>131737833</v>
       </c>
       <c r="B4" t="n">
-        <v>96685</v>
+        <v>96688</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131726428</v>
       </c>
       <c r="B5" t="n">
-        <v>79934</v>
+        <v>79936</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13873-2026 artfynd.xlsx
+++ b/artfynd/A 13873-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131726429</v>
+        <v>131726431</v>
       </c>
       <c r="B2" t="n">
-        <v>79936</v>
+        <v>96783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -748,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -758,7 +759,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131726431</v>
+        <v>131737833</v>
       </c>
       <c r="B3" t="n">
-        <v>96688</v>
+        <v>96783</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,23 +815,19 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupvik, Djupvik, Srm</t>
+          <t>Djupvik, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584591</v>
+        <v>584546</v>
       </c>
       <c r="R3" t="n">
-        <v>6546418</v>
+        <v>6546482</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,27 +854,18 @@
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>10:32</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -896,48 +884,51 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131737833</v>
+        <v>131726428</v>
       </c>
       <c r="B4" t="n">
-        <v>96688</v>
+        <v>79992</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupvik, Srm</t>
+          <t>Djupvik, Djupvik, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584546</v>
+        <v>584450</v>
       </c>
       <c r="R4" t="n">
-        <v>6546482</v>
+        <v>6546536</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,18 +955,27 @@
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,10 +994,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131726428</v>
+        <v>131726429</v>
       </c>
       <c r="B5" t="n">
-        <v>79936</v>
+        <v>79992</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>584450</v>
+        <v>584591</v>
       </c>
       <c r="R5" t="n">
-        <v>6546536</v>
+        <v>6546418</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,6 +1101,297 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>131737824</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78973</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>228595</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulvit renlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cladonia arbuscula</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Wallr.) Flot.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Djupvik, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>584546</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6546482</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131737826</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79050</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228654</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Grå renlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cladonia rangiferina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Djupvik, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>584546</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6546482</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>131737830</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79057</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228659</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fönsterlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cladonia stellaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Opiz) Pouzar &amp; Vezda</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Djupvik, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>584546</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6546482</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sköldinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Göran Ekström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 13873-2026 artfynd.xlsx
+++ b/artfynd/A 13873-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131726431</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737833</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131726428</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1101,6 +1121,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131726429</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737824</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1295,6 +1325,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737826</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1392,8 +1427,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131737830</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>